--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486455_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486455_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1431</v>
+        <v>3.519</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4918</v>
+        <v>4.1759</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3487</v>
+        <v>-0.6569</v>
       </c>
       <c r="G2" t="n">
         <v>2.1983</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0297</v>
+        <v>0.4056</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5418</v>
+        <v>0.2259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4879</v>
+        <v>0.1796</v>
       </c>
       <c r="V2" t="n">
         <v>-1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9411</v>
+        <v>3.1522</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8608</v>
+        <v>3.0411</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0803</v>
+        <v>0.1111</v>
       </c>
       <c r="G3" t="n">
         <v>0.5725</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4589</v>
+        <v>-0.2478</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0769</v>
+        <v>0.1034</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4971</v>
+        <v>2.0015</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0835</v>
+        <v>1.0572</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5805</v>
+        <v>0.9442</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1145</v>
+        <v>1.4247</v>
       </c>
       <c r="H4" t="n">
-        <v>1.621</v>
+        <v>1.2621</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7355</v>
+        <v>0.1626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2092</v>
+        <v>2.5269</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1383</v>
+        <v>2.4089</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9292</v>
+        <v>0.118</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3237</v>
+        <v>-1.1022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5173</v>
+        <v>-1.1468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1936</v>
+        <v>0.0446</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9591</v>
+        <v>-0.2932</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5997</v>
+        <v>-0.3821</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3594</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1872</v>
+        <v>1.0787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8933</v>
+        <v>0.6683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.294</v>
+        <v>0.4104</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4848</v>
+        <v>1.0757</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8306</v>
+        <v>-0.581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6542</v>
+        <v>1.6567</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1072</v>
+        <v>2.311</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6665</v>
+        <v>0.1674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4407</v>
+        <v>2.1436</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3776</v>
+        <v>-1.2353</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1641</v>
+        <v>-0.7484</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2136</v>
+        <v>-0.4869</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0499</v>
+        <v>-0.6495</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8736</v>
+        <v>-0.5552</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1763</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0517</v>
+        <v>0.8844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.333</v>
+        <v>-0.4188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7187</v>
+        <v>1.3031</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0757</v>
+        <v>-0.1145</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.581</v>
+        <v>1.621</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6567</v>
+        <v>-1.7355</v>
       </c>
       <c r="J6" t="n">
-        <v>2.311</v>
+        <v>0.2092</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1674</v>
+        <v>2.1383</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1436</v>
+        <v>-1.9292</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2353</v>
+        <v>-0.3237</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7484</v>
+        <v>-0.5173</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>0.1936</v>
       </c>
       <c r="P6" t="n">
         <v>0.6525</v>
@@ -922,28 +922,28 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6766</v>
+        <v>0.3464</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8904</v>
+        <v>0.2644</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2139</v>
+        <v>0.082</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0274</v>
+        <v>0.7393</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2064</v>
+        <v>-0.1983</v>
       </c>
       <c r="F7" t="n">
-        <v>0.821</v>
+        <v>0.9376</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4247</v>
+        <v>-0.4425</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2621</v>
+        <v>1.3655</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1626</v>
+        <v>-1.8081</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5269</v>
+        <v>-0.5149</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4089</v>
+        <v>1.7004</v>
       </c>
       <c r="L7" t="n">
-        <v>0.118</v>
+        <v>-2.2152</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1022</v>
+        <v>0.0723</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1468</v>
+        <v>-0.3348</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0446</v>
+        <v>0.4072</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2673</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2329</v>
+        <v>0.1214</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0344</v>
+        <v>-0.0499</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.4997</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4794</v>
+        <v>0.547</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5275</v>
+        <v>-0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0069</v>
+        <v>1.161</v>
       </c>
       <c r="G8" t="n">
         <v>-0.08409999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1508</v>
+        <v>0.2184</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1971</v>
+        <v>0.1106</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V8" t="n">
         <v>0.1952</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3287</v>
+        <v>0.4242</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6705</v>
+        <v>0.2227</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9992</v>
+        <v>0.2015</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4425</v>
+        <v>1.4848</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3655</v>
+        <v>0.8306</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8081</v>
+        <v>0.6542</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5149</v>
+        <v>1.1072</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7004</v>
+        <v>0.6665</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2152</v>
+        <v>0.4407</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0723</v>
+        <v>0.3776</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3348</v>
+        <v>0.1641</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4072</v>
+        <v>0.2136</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6101</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3391</v>
+        <v>0.2869</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3509</v>
+        <v>0.2031</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0118</v>
+        <v>0.0838</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4997</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1119</v>
+        <v>0.2853</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.032</v>
+        <v>0.0798</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1439</v>
+        <v>0.2055</v>
       </c>
       <c r="G10" t="n">
         <v>0.6325</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3254</v>
+        <v>-0.152</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5141</v>
+        <v>-0.2414</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4213</v>
+        <v>-0.3288</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0723</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4419</v>
+        <v>-0.1691</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.0252</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0383</v>
+        <v>-1.4997</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8648</v>
+        <v>-1.5728</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1735</v>
+        <v>0.0731</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8567</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.702</v>
+        <v>-0.1634</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8989</v>
+        <v>-0.6068</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1968</v>
+        <v>0.4434</v>
       </c>
       <c r="V12" t="n">
         <v>1.5204</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8117</v>
+        <v>-2.8021</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7526</v>
+        <v>-4.0821</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9409</v>
+        <v>1.28</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2963</v>
@@ -1468,13 +1468,13 @@
         <v>2.8276</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2555</v>
+        <v>-1.2459</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5069</v>
+        <v>-0.8364</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.4095</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.403499999999999</v>
+        <v>8.088399999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>1.761599999999998</v>
+        <v>2.446400000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6419</v>
+        <v>5.6418</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5220999999999996</v>
+        <v>0.5221000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.2154</v>
+        <v>-5.215400000000001</v>
       </c>
       <c r="I14" t="n">
         <v>5.7374</v>
@@ -1534,7 +1534,7 @@
         <v>-8.730899999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7687999999999998</v>
+        <v>0.7688</v>
       </c>
       <c r="P14" t="n">
         <v>11.9629</v>
@@ -1546,13 +1546,13 @@
         <v>20.6633</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2772</v>
+        <v>-1.5921</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0187</v>
+        <v>-1.3336</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2584</v>
+        <v>-0.2585999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8043</v>
@@ -1561,7 +1561,7 @@
         <v>3.9962</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8006</v>
+        <v>-6.800599999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.148</v>
+        <v>3.146</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8467</v>
+        <v>2.6291</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3012</v>
+        <v>0.517</v>
       </c>
       <c r="G15" t="n">
         <v>1.6312</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8307</v>
+        <v>0.1673</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0034</v>
+        <v>-0.2211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1727</v>
+        <v>0.3884</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8351</v>
+        <v>1.0321</v>
       </c>
       <c r="E16" t="n">
-        <v>1.824</v>
+        <v>0.8194</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0111</v>
+        <v>0.2127</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0496</v>
+        <v>3.485</v>
       </c>
       <c r="H16" t="n">
-        <v>0.003</v>
+        <v>1.7821</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0527</v>
+        <v>1.7029</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2885</v>
+        <v>4.0772</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9188</v>
+        <v>1.5694</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6303</v>
+        <v>2.5078</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3381</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.2127</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4224</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7401</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7999</v>
+        <v>0.2872</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8857</v>
+        <v>0.0048</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9142</v>
+        <v>0.2824</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8249</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0599</v>
+        <v>1.0182</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2936</v>
+        <v>1.377</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7663</v>
+        <v>-0.3588</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6389</v>
+        <v>-1.0496</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0955</v>
+        <v>0.003</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4566</v>
+        <v>-1.0527</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9976</v>
+        <v>0.2885</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8828</v>
+        <v>0.9188</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1147</v>
+        <v>-0.6303</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3587</v>
+        <v>-1.3381</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2127</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5714</v>
+        <v>-0.4224</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.029</v>
+        <v>0.983</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.399</v>
+        <v>0.4386</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4279</v>
+        <v>0.5444</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3904</v>
+        <v>2.8249</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5736</v>
+        <v>0.8942</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4841</v>
+        <v>0.4054</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.4889</v>
       </c>
       <c r="G18" t="n">
-        <v>3.485</v>
+        <v>1.6389</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7821</v>
+        <v>2.0955</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7029</v>
+        <v>-0.4566</v>
       </c>
       <c r="J18" t="n">
-        <v>4.0772</v>
+        <v>1.9976</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5694</v>
+        <v>1.8828</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5078</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3587</v>
       </c>
       <c r="N18" t="n">
         <v>0.2127</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.5714</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1714</v>
+        <v>-0.1367</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.2872</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1591</v>
+        <v>0.1505</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.1746</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1574</v>
+        <v>0.166</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2415</v>
+        <v>-1.3406</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9094</v>
+        <v>0.732</v>
       </c>
       <c r="H19" t="n">
-        <v>0.003</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9125</v>
+        <v>0.8112</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9314</v>
+        <v>2.1187</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5387</v>
+        <v>0.5871</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4702</v>
+        <v>1.5316</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.978</v>
+        <v>-1.3867</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5357</v>
+        <v>-0.6663</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4423</v>
+        <v>-0.7204</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9576</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4577</v>
+        <v>0.4191</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8963</v>
+        <v>0.2223</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5614</v>
+        <v>0.1968</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3252</v>
+        <v>-0.5857</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9704</v>
+        <v>-1.4753</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2777</v>
+        <v>-1.2954</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2481</v>
+        <v>-0.1799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.732</v>
+        <v>-1.9094</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8112</v>
+        <v>-1.9125</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1187</v>
+        <v>-0.9314</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5871</v>
+        <v>0.5387</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5316</v>
+        <v>-1.4702</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3867</v>
+        <v>-0.978</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6663</v>
+        <v>-0.5357</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7204</v>
+        <v>-0.4423</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6233</v>
+        <v>1.0665</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3341</v>
+        <v>0.4434</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2892</v>
+        <v>0.6231</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5857</v>
+        <v>1.3252</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5857</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2241</v>
+        <v>-1.6768</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0825</v>
+        <v>-1.4119</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1416</v>
+        <v>-0.2649</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5472</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3718</v>
+        <v>0.1754</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7294</v>
+        <v>-0.0589</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3576</v>
+        <v>0.2343</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7458</v>
+        <v>-3.6418</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5264</v>
+        <v>-2.6382</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2194</v>
+        <v>-1.0036</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4019</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2792</v>
+        <v>-0.1751</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1406</v>
+        <v>0.0288</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4198</v>
+        <v>-0.204</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9957</v>
+        <v>-5.5256</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9167</v>
+        <v>-5.6932</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0789</v>
+        <v>0.1676</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1009</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9796</v>
+        <v>-0.5095</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.536</v>
+        <v>-0.3124</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4437</v>
+        <v>-0.1971</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4035</v>
+        <v>-7.403600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.642099999999999</v>
+        <v>-5.6418</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7615</v>
+        <v>-1.7616</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5219000000000003</v>
@@ -2329,10 +2329,10 @@
         <v>2.2772</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2583999999999999</v>
+        <v>0.2583</v>
       </c>
       <c r="U24" t="n">
-        <v>2.0186</v>
+        <v>2.0188</v>
       </c>
       <c r="V24" t="n">
         <v>2.8043</v>
